--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6194" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6195" uniqueCount="734">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -945,7 +945,10 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-encounter-class|0.1.0</t>
+    <t>Classification of the encounter.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1103,12 +1106,6 @@
   </si>
   <si>
     <t>inpatient | outpatient | ambulatory | emergency +.</t>
-  </si>
-  <si>
-    <t>Classification of the encounter.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -6817,9 +6814,11 @@
       <c r="X37" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y37" s="2"/>
+      <c r="Y37" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6855,21 +6854,21 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6978,10 +6977,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7092,10 +7091,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7121,16 +7120,16 @@
         <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -7179,7 +7178,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7197,21 +7196,21 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7237,13 +7236,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7293,7 +7292,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7311,21 +7310,21 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7351,14 +7350,14 @@
         <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7407,7 +7406,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7425,21 +7424,21 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7465,14 +7464,14 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7521,7 +7520,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7539,21 +7538,21 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7576,19 +7575,19 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7637,7 +7636,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7655,21 +7654,21 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7695,10 +7694,10 @@
         <v>279</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7749,7 +7748,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7778,10 +7777,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7890,10 +7889,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8004,10 +8003,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8120,10 +8119,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8149,10 +8148,10 @@
         <v>146</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8182,10 +8181,10 @@
         <v>150</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>351</v>
+        <v>298</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>352</v>
+        <v>299</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -8203,7 +8202,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>88</v>
@@ -8232,10 +8231,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8261,10 +8260,10 @@
         <v>254</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8315,7 +8314,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>88</v>
@@ -8344,10 +8343,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8373,13 +8372,13 @@
         <v>228</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8409,7 +8408,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8427,7 +8426,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8442,24 +8441,24 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8485,10 +8484,10 @@
         <v>228</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8518,11 +8517,11 @@
         <v>158</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8539,7 +8538,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8554,7 +8553,7 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>106</v>
@@ -8563,15 +8562,15 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8597,10 +8596,10 @@
         <v>228</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8630,11 +8629,11 @@
         <v>158</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8651,7 +8650,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8669,25 +8668,25 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>376</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8706,16 +8705,16 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8765,7 +8764,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8780,24 +8779,24 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8820,13 +8819,13 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8877,7 +8876,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8892,28 +8891,28 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8932,13 +8931,13 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8989,7 +8988,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9004,10 +9003,10 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
@@ -9018,10 +9017,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9047,10 +9046,10 @@
         <v>279</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9101,7 +9100,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9116,24 +9115,24 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9242,10 +9241,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9356,10 +9355,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9472,10 +9471,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9501,13 +9500,13 @@
         <v>228</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9536,10 +9535,10 @@
         <v>150</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9557,7 +9556,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9572,24 +9571,24 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9615,10 +9614,10 @@
         <v>254</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9669,7 +9668,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9687,21 +9686,21 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9724,13 +9723,13 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9781,7 +9780,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9796,24 +9795,24 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>430</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9922,10 +9921,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10036,13 +10035,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C66" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>80</v>
@@ -10064,13 +10063,13 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10150,10 +10149,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10262,10 +10261,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10273,7 +10272,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>79</v>
@@ -10374,13 +10373,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>80</v>
@@ -10488,10 +10487,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10600,10 +10599,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10712,10 +10711,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10741,13 +10740,13 @@
         <v>130</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10755,7 +10754,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>80</v>
@@ -10797,7 +10796,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>88</v>
@@ -10826,10 +10825,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10855,10 +10854,10 @@
         <v>168</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10870,7 +10869,7 @@
         <v>80</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>80</v>
@@ -10889,25 +10888,25 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10936,13 +10935,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C74" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>80</v>
@@ -10967,7 +10966,7 @@
         <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>194</v>
@@ -11050,10 +11049,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11162,10 +11161,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11274,10 +11273,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11303,13 +11302,13 @@
         <v>130</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11317,7 +11316,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>80</v>
@@ -11359,7 +11358,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>88</v>
@@ -11388,10 +11387,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11417,10 +11416,10 @@
         <v>228</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11471,7 +11470,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11500,13 +11499,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11531,7 +11530,7 @@
         <v>109</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M79" t="s" s="2">
         <v>194</v>
@@ -11614,10 +11613,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11726,10 +11725,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11838,10 +11837,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11867,13 +11866,13 @@
         <v>130</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11881,7 +11880,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>80</v>
@@ -11923,7 +11922,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>88</v>
@@ -11952,10 +11951,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11978,13 +11977,13 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12035,7 +12034,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12064,10 +12063,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12093,13 +12092,13 @@
         <v>130</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12107,7 +12106,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>80</v>
@@ -12149,7 +12148,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>88</v>
@@ -12178,10 +12177,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12204,13 +12203,13 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12261,7 +12260,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12290,13 +12289,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>80</v>
@@ -12318,13 +12317,13 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12404,10 +12403,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12516,10 +12515,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12527,7 +12526,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>79</v>
@@ -12628,13 +12627,13 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>80</v>
@@ -12742,10 +12741,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12854,10 +12853,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12966,10 +12965,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12995,13 +12994,13 @@
         <v>130</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13009,7 +13008,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>80</v>
@@ -13051,7 +13050,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>88</v>
@@ -13080,10 +13079,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13109,10 +13108,10 @@
         <v>168</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13124,7 +13123,7 @@
         <v>80</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>80</v>
@@ -13143,25 +13142,25 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13190,13 +13189,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>80</v>
@@ -13221,7 +13220,7 @@
         <v>109</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>194</v>
@@ -13304,10 +13303,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13416,10 +13415,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13528,10 +13527,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13557,13 +13556,13 @@
         <v>130</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13571,7 +13570,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>80</v>
@@ -13613,7 +13612,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>88</v>
@@ -13642,10 +13641,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13671,10 +13670,10 @@
         <v>228</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13725,7 +13724,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13754,13 +13753,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>80</v>
@@ -13785,7 +13784,7 @@
         <v>109</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>194</v>
@@ -13868,10 +13867,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13980,10 +13979,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14092,10 +14091,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14121,13 +14120,13 @@
         <v>130</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14135,7 +14134,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>80</v>
@@ -14177,7 +14176,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>88</v>
@@ -14206,10 +14205,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14232,13 +14231,13 @@
         <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14289,7 +14288,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14318,10 +14317,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14347,13 +14346,13 @@
         <v>130</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14361,7 +14360,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>80</v>
@@ -14403,7 +14402,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>88</v>
@@ -14432,10 +14431,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14458,13 +14457,13 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14515,7 +14514,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14544,13 +14543,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C106" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>80</v>
@@ -14572,13 +14571,13 @@
         <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14658,10 +14657,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14770,10 +14769,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14781,7 +14780,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>79</v>
@@ -14882,13 +14881,13 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>80</v>
@@ -14996,10 +14995,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15108,10 +15107,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15220,10 +15219,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15249,13 +15248,13 @@
         <v>130</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15263,7 +15262,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>80</v>
@@ -15305,7 +15304,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>88</v>
@@ -15334,10 +15333,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15363,10 +15362,10 @@
         <v>168</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15378,7 +15377,7 @@
         <v>80</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>80</v>
@@ -15397,25 +15396,25 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF113" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15444,13 +15443,13 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>80</v>
@@ -15475,7 +15474,7 @@
         <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>194</v>
@@ -15558,10 +15557,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15670,10 +15669,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15782,10 +15781,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15811,13 +15810,13 @@
         <v>130</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15825,7 +15824,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>80</v>
@@ -15867,7 +15866,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>88</v>
@@ -15896,10 +15895,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15925,10 +15924,10 @@
         <v>228</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -15979,7 +15978,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16008,13 +16007,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>80</v>
@@ -16039,7 +16038,7 @@
         <v>109</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>194</v>
@@ -16122,10 +16121,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16234,10 +16233,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16346,10 +16345,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16375,13 +16374,13 @@
         <v>130</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16389,7 +16388,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>80</v>
@@ -16431,7 +16430,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>88</v>
@@ -16460,10 +16459,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16486,13 +16485,13 @@
         <v>80</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16543,7 +16542,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16572,10 +16571,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16601,13 +16600,13 @@
         <v>130</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -16615,7 +16614,7 @@
       </c>
       <c r="Q124" s="2"/>
       <c r="R124" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S124" t="s" s="2">
         <v>80</v>
@@ -16657,7 +16656,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>88</v>
@@ -16686,10 +16685,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16712,13 +16711,13 @@
         <v>80</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16769,7 +16768,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16798,10 +16797,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16827,13 +16826,13 @@
         <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16883,16 +16882,16 @@
         <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI126" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>100</v>
@@ -16912,10 +16911,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16941,13 +16940,13 @@
         <v>130</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16976,28 +16975,28 @@
         <v>150</v>
       </c>
       <c r="Y127" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="Z127" t="s" s="2">
+      <c r="AA127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF127" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17026,10 +17025,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17055,13 +17054,13 @@
         <v>208</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17111,7 +17110,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17129,7 +17128,7 @@
         <v>80</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>80</v>
@@ -17140,10 +17139,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17169,13 +17168,13 @@
         <v>102</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17225,7 +17224,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17254,10 +17253,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17280,13 +17279,13 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17337,7 +17336,7 @@
         <v>80</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17352,24 +17351,24 @@
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AL130" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>558</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17395,13 +17394,13 @@
         <v>254</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17451,7 +17450,7 @@
         <v>80</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17466,24 +17465,24 @@
         <v>100</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AL131" t="s" s="2">
+      <c r="AM131" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AM131" t="s" s="2">
+      <c r="AN131" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>566</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17506,16 +17505,16 @@
         <v>80</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17565,7 +17564,7 @@
         <v>80</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17580,28 +17579,28 @@
         <v>100</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AL132" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>573</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -17623,13 +17622,13 @@
         <v>228</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17658,11 +17657,11 @@
         <v>172</v>
       </c>
       <c r="Y133" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="Z133" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="Z133" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="AA133" t="s" s="2">
         <v>80</v>
       </c>
@@ -17679,7 +17678,7 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17694,28 +17693,28 @@
         <v>100</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AL133" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="AM133" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AM133" t="s" s="2">
+      <c r="AN133" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>584</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -17734,16 +17733,16 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L134" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="M134" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17793,7 +17792,7 @@
         <v>80</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17808,24 +17807,24 @@
         <v>100</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AL134" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AL134" t="s" s="2">
+      <c r="AM134" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AM134" t="s" s="2">
+      <c r="AN134" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>584</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17851,10 +17850,10 @@
         <v>279</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17905,7 +17904,7 @@
         <v>80</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17923,7 +17922,7 @@
         <v>80</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>80</v>
@@ -17934,10 +17933,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18046,10 +18045,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18160,10 +18159,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18276,14 +18275,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -18302,16 +18301,16 @@
         <v>89</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M139" t="s" s="2">
-        <v>599</v>
-      </c>
       <c r="N139" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18361,7 +18360,7 @@
         <v>80</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>88</v>
@@ -18376,24 +18375,24 @@
         <v>100</v>
       </c>
       <c r="AK139" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AL139" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="AL139" t="s" s="2">
+      <c r="AM139" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN139" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>602</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18419,10 +18418,10 @@
         <v>228</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18452,11 +18451,11 @@
         <v>172</v>
       </c>
       <c r="Y140" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="Z140" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="Z140" t="s" s="2">
-        <v>607</v>
-      </c>
       <c r="AA140" t="s" s="2">
         <v>80</v>
       </c>
@@ -18473,7 +18472,7 @@
         <v>80</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18502,10 +18501,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18528,13 +18527,13 @@
         <v>80</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18585,7 +18584,7 @@
         <v>80</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18603,7 +18602,7 @@
         <v>80</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>80</v>
@@ -18614,10 +18613,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18640,16 +18639,16 @@
         <v>80</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18699,7 +18698,7 @@
         <v>80</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18717,7 +18716,7 @@
         <v>80</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>80</v>
@@ -18728,10 +18727,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18757,13 +18756,13 @@
         <v>279</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18813,7 +18812,7 @@
         <v>80</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18831,7 +18830,7 @@
         <v>80</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>80</v>
@@ -18842,10 +18841,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18954,10 +18953,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19068,10 +19067,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19184,10 +19183,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19213,10 +19212,10 @@
         <v>208</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19267,7 +19266,7 @@
         <v>80</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19291,15 +19290,15 @@
         <v>80</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19408,10 +19407,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19522,10 +19521,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19638,10 +19637,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19670,7 +19669,7 @@
         <v>229</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>231</v>
@@ -19752,10 +19751,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19784,7 +19783,7 @@
         <v>237</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>239</v>
@@ -19797,7 +19796,7 @@
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="S152" t="s" s="2">
         <v>80</v>
@@ -19868,10 +19867,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19982,10 +19981,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20094,10 +20093,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20208,10 +20207,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20234,13 +20233,13 @@
         <v>80</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -20291,7 +20290,7 @@
         <v>80</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20309,7 +20308,7 @@
         <v>80</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>80</v>
@@ -20320,10 +20319,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20349,10 +20348,10 @@
         <v>228</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -20383,7 +20382,7 @@
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>80</v>
@@ -20401,7 +20400,7 @@
         <v>80</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20419,21 +20418,21 @@
         <v>80</v>
       </c>
       <c r="AL157" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN157" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>652</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20459,10 +20458,10 @@
         <v>228</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -20492,11 +20491,11 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="Z158" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="Z158" t="s" s="2">
-        <v>657</v>
-      </c>
       <c r="AA158" t="s" s="2">
         <v>80</v>
       </c>
@@ -20513,7 +20512,7 @@
         <v>80</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20537,15 +20536,15 @@
         <v>80</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20571,16 +20570,16 @@
         <v>228</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>80</v>
@@ -20608,11 +20607,11 @@
         <v>158</v>
       </c>
       <c r="Y159" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="Z159" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="Z159" t="s" s="2">
-        <v>665</v>
-      </c>
       <c r="AA159" t="s" s="2">
         <v>80</v>
       </c>
@@ -20629,7 +20628,7 @@
         <v>80</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20647,21 +20646,21 @@
         <v>80</v>
       </c>
       <c r="AL159" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN159" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>667</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20687,10 +20686,10 @@
         <v>228</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -20720,11 +20719,11 @@
         <v>172</v>
       </c>
       <c r="Y160" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="Z160" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="Z160" t="s" s="2">
-        <v>672</v>
-      </c>
       <c r="AA160" t="s" s="2">
         <v>80</v>
       </c>
@@ -20741,7 +20740,7 @@
         <v>80</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20759,21 +20758,21 @@
         <v>80</v>
       </c>
       <c r="AL160" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN160" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>674</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20799,10 +20798,10 @@
         <v>228</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -20832,11 +20831,11 @@
         <v>172</v>
       </c>
       <c r="Y161" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="Z161" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="Z161" t="s" s="2">
-        <v>679</v>
-      </c>
       <c r="AA161" t="s" s="2">
         <v>80</v>
       </c>
@@ -20853,7 +20852,7 @@
         <v>80</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20871,21 +20870,21 @@
         <v>80</v>
       </c>
       <c r="AL161" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN161" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>681</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20908,13 +20907,13 @@
         <v>80</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20965,7 +20964,7 @@
         <v>80</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20983,21 +20982,21 @@
         <v>80</v>
       </c>
       <c r="AL162" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN162" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>686</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21023,10 +21022,10 @@
         <v>228</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -21057,7 +21056,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>80</v>
@@ -21075,7 +21074,7 @@
         <v>80</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21093,21 +21092,21 @@
         <v>80</v>
       </c>
       <c r="AL163" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AM163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN163" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>692</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21133,13 +21132,13 @@
         <v>279</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -21189,7 +21188,7 @@
         <v>80</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21207,7 +21206,7 @@
         <v>80</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>80</v>
@@ -21218,10 +21217,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21330,10 +21329,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21444,10 +21443,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21560,10 +21559,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21586,13 +21585,13 @@
         <v>80</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="L168" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="L168" t="s" s="2">
+      <c r="M168" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -21643,7 +21642,7 @@
         <v>80</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>88</v>
@@ -21658,24 +21657,24 @@
         <v>100</v>
       </c>
       <c r="AK168" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM168" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="AL168" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AM168" t="s" s="2">
+      <c r="AN168" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>707</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21701,13 +21700,13 @@
         <v>168</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21736,11 +21735,11 @@
         <v>222</v>
       </c>
       <c r="Y169" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="Z169" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="Z169" t="s" s="2">
-        <v>713</v>
-      </c>
       <c r="AA169" t="s" s="2">
         <v>80</v>
       </c>
@@ -21757,7 +21756,7 @@
         <v>80</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21775,7 +21774,7 @@
         <v>80</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>80</v>
@@ -21786,10 +21785,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21815,13 +21814,13 @@
         <v>228</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -21851,7 +21850,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>80</v>
@@ -21869,7 +21868,7 @@
         <v>80</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -21898,10 +21897,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21927,10 +21926,10 @@
         <v>254</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -21981,7 +21980,7 @@
         <v>80</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -21999,7 +21998,7 @@
         <v>80</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>80</v>
@@ -22010,10 +22009,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22039,10 +22038,10 @@
         <v>261</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -22093,7 +22092,7 @@
         <v>80</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22108,24 +22107,24 @@
         <v>100</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AL172" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN172" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="AM172" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>727</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22148,16 +22147,16 @@
         <v>80</v>
       </c>
       <c r="K173" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="L173" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="L173" t="s" s="2">
+      <c r="M173" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -22207,7 +22206,7 @@
         <v>80</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22222,10 +22221,10 @@
         <v>100</v>
       </c>
       <c r="AK173" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AL173" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="AL173" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6195" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6196" uniqueCount="735">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2032,7 +2032,10 @@
     <t>From where patient was admitted (physician referral, transfer).</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-entree-cisis|20260619134043</t>
+    <t>From where the patient was admitted.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -20378,11 +20381,13 @@
         <v>80</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y157" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>649</v>
+      </c>
       <c r="Z157" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>80</v>
@@ -20418,21 +20423,21 @@
         <v>80</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20458,10 +20463,10 @@
         <v>228</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -20491,10 +20496,10 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>80</v>
@@ -20512,7 +20517,7 @@
         <v>80</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20536,15 +20541,15 @@
         <v>80</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20570,16 +20575,16 @@
         <v>228</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>80</v>
@@ -20607,10 +20612,10 @@
         <v>158</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>80</v>
@@ -20628,7 +20633,7 @@
         <v>80</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20646,21 +20651,21 @@
         <v>80</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20686,10 +20691,10 @@
         <v>228</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -20719,10 +20724,10 @@
         <v>172</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>80</v>
@@ -20740,7 +20745,7 @@
         <v>80</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20758,21 +20763,21 @@
         <v>80</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20798,10 +20803,10 @@
         <v>228</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -20831,10 +20836,10 @@
         <v>172</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>80</v>
@@ -20852,7 +20857,7 @@
         <v>80</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20870,21 +20875,21 @@
         <v>80</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20910,10 +20915,10 @@
         <v>642</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20964,7 +20969,7 @@
         <v>80</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20982,21 +20987,21 @@
         <v>80</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21022,10 +21027,10 @@
         <v>228</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -21056,7 +21061,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>80</v>
@@ -21074,7 +21079,7 @@
         <v>80</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21092,21 +21097,21 @@
         <v>80</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21132,13 +21137,13 @@
         <v>279</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -21188,7 +21193,7 @@
         <v>80</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21206,7 +21211,7 @@
         <v>80</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>80</v>
@@ -21217,10 +21222,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21329,10 +21334,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21443,10 +21448,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21559,10 +21564,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21585,13 +21590,13 @@
         <v>80</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -21642,7 +21647,7 @@
         <v>80</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>88</v>
@@ -21657,24 +21662,24 @@
         <v>100</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>427</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21700,13 +21705,13 @@
         <v>168</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21735,10 +21740,10 @@
         <v>222</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>80</v>
@@ -21756,7 +21761,7 @@
         <v>80</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21774,7 +21779,7 @@
         <v>80</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>80</v>
@@ -21785,10 +21790,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21814,13 +21819,13 @@
         <v>228</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -21850,7 +21855,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>80</v>
@@ -21868,7 +21873,7 @@
         <v>80</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -21897,10 +21902,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21926,10 +21931,10 @@
         <v>254</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -21980,7 +21985,7 @@
         <v>80</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -22009,10 +22014,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22038,10 +22043,10 @@
         <v>261</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -22092,7 +22097,7 @@
         <v>80</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22110,21 +22115,21 @@
         <v>426</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22147,16 +22152,16 @@
         <v>80</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -22206,7 +22211,7 @@
         <v>80</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22221,10 +22226,10 @@
         <v>100</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2156,7 +2156,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-sortie-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-sortie-cisis|20260716085852</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
